--- a/data/crit_values.xlsx
+++ b/data/crit_values.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="27">
   <si>
     <t>id</t>
   </si>
@@ -2766,6 +2766,424 @@
         <v>26</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>12</v>
+      </c>
+      <c r="B70" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="C70" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="D70" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="F70" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="G70" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="H70" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="J70" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="K70" t="n" s="2">
+        <v>45180.0</v>
+      </c>
+      <c r="L70" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>13</v>
+      </c>
+      <c r="B71" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="C71" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="D71" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="E71" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="F71" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G71" t="n">
+        <v>53.0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="I71" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="J71" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="K71" t="n" s="2">
+        <v>45180.0</v>
+      </c>
+      <c r="L71" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>14</v>
+      </c>
+      <c r="B72" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="C72" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="D72" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="E72" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="F72" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G72" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="H72" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="I72" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="J72" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="K72" t="n" s="2">
+        <v>45180.0</v>
+      </c>
+      <c r="L72" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="C73" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="D73" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="E73" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="F73" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="H73" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="I73" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="J73" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="K73" t="n" s="2">
+        <v>45180.0</v>
+      </c>
+      <c r="L73" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>16</v>
+      </c>
+      <c r="B74" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="C74" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="D74" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="E74" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="F74" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="G74" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="H74" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="I74" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="J74" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="K74" t="n" s="2">
+        <v>45180.0</v>
+      </c>
+      <c r="L74" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>17</v>
+      </c>
+      <c r="B75" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="C75" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="D75" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="E75" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="F75" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="H75" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="I75" t="n">
+        <v>57.0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="K75" t="n" s="2">
+        <v>45180.0</v>
+      </c>
+      <c r="L75" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>18</v>
+      </c>
+      <c r="B76" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="C76" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="D76" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="F76" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="I76" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="J76" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="K76" t="n" s="2">
+        <v>45180.0</v>
+      </c>
+      <c r="L76" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>19</v>
+      </c>
+      <c r="B77" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C77" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="D77" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="E77" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="F77" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="G77" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="H77" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="I77" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="J77" t="n">
+        <v>68.6</v>
+      </c>
+      <c r="K77" t="n" s="2">
+        <v>45180.0</v>
+      </c>
+      <c r="L77" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>20</v>
+      </c>
+      <c r="B78" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="C78" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="D78" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="E78" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="F78" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="G78" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="H78" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="I78" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="J78" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="K78" t="n" s="2">
+        <v>45180.0</v>
+      </c>
+      <c r="L78" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>21</v>
+      </c>
+      <c r="B79" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="C79" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="E79" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="F79" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="G79" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="H79" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="I79" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="J79" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="K79" t="n" s="2">
+        <v>45180.0</v>
+      </c>
+      <c r="L79" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>22</v>
+      </c>
+      <c r="B80" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="C80" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="D80" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="E80" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="F80" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="G80" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H80" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="I80" t="n">
+        <v>67.6</v>
+      </c>
+      <c r="J80" t="n">
+        <v>90.6</v>
+      </c>
+      <c r="K80" t="n" s="2">
+        <v>45180.0</v>
+      </c>
+      <c r="L80" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/data/crit_values.xlsx
+++ b/data/crit_values.xlsx
@@ -1,13 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Joe/Documents/College/02- R code/2- heating/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CA5FB5-16D0-6B40-A772-282B3BBDDF77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" r:id="rId3" sheetId="1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -80,9 +88,6 @@
     <t>Quercus montana</t>
   </si>
   <si>
-    <t>Ulmus americana</t>
-  </si>
-  <si>
     <t>TN</t>
   </si>
   <si>
@@ -94,17 +99,20 @@
   <si>
     <t>MI</t>
   </si>
+  <si>
+    <t>Ulmus rubra</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,7 +124,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -131,20 +139,330 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L80"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -182,3009 +500,3009 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>43.7</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>47.6</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>51.1</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>50.9</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>51.9</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>52.5</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>53.4</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>55.6</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>58.4</v>
       </c>
-      <c r="K2" t="n" s="2">
-        <v>44733.0</v>
+      <c r="K2" s="1">
+        <v>44733</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>42.3</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>45.1</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>47.9</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>51.2</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>52.1</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>53.2</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>55.3</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>58.4</v>
       </c>
-      <c r="J3" t="n">
-        <v>62.0</v>
-      </c>
-      <c r="K3" t="n" s="2">
-        <v>44733.0</v>
+      <c r="J3">
+        <v>62</v>
+      </c>
+      <c r="K3" s="1">
+        <v>44733</v>
       </c>
       <c r="L3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>41.8</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>44.3</v>
       </c>
-      <c r="D4" t="n">
-        <v>47.0</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4">
+        <v>47</v>
+      </c>
+      <c r="E4">
         <v>50.9</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>51.9</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>53.5</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>54.4</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>58.7</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>62.7</v>
       </c>
-      <c r="K4" t="n" s="2">
-        <v>44733.0</v>
+      <c r="K4" s="1">
+        <v>44733</v>
       </c>
       <c r="L4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="C5" t="n">
+      <c r="B5">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="C5">
         <v>42.4</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>44.7</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>50.9</v>
       </c>
-      <c r="F5" t="n">
-        <v>52.0</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="F5">
+        <v>52</v>
+      </c>
+      <c r="G5">
         <v>53.2</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>57.2</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>60.5</v>
       </c>
-      <c r="J5" t="n">
-        <v>64.1</v>
-      </c>
-      <c r="K5" t="n" s="2">
-        <v>44733.0</v>
+      <c r="J5">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="K5" s="1">
+        <v>44733</v>
       </c>
       <c r="L5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="C6" t="n">
+      <c r="B6">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="C6">
         <v>43.5</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>47.4</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>51.2</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>52.4</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>54.1</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>56.9</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>60.5</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>63.4</v>
       </c>
-      <c r="K6" t="n" s="2">
-        <v>44733.0</v>
+      <c r="K6" s="1">
+        <v>44733</v>
       </c>
       <c r="L6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="C7">
         <v>43.5</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>46.5</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>49.7</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>50.7</v>
       </c>
-      <c r="G7" t="n">
-        <v>52.0</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="G7">
+        <v>52</v>
+      </c>
+      <c r="H7">
         <v>53.7</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>57.2</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>61.8</v>
       </c>
-      <c r="K7" t="n" s="2">
-        <v>44733.0</v>
+      <c r="K7" s="1">
+        <v>44733</v>
       </c>
       <c r="L7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>41.8</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>44.4</v>
       </c>
-      <c r="D8" t="n">
-        <v>47.0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>51.0</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="D8">
+        <v>47</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>51</v>
+      </c>
+      <c r="G8">
         <v>52.1</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>52.7</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>56.7</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>60.2</v>
       </c>
-      <c r="K8" t="n" s="2">
-        <v>44733.0</v>
+      <c r="K8" s="1">
+        <v>44733</v>
       </c>
       <c r="L8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
-      <c r="B9" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B9">
+        <v>40</v>
+      </c>
+      <c r="C9">
         <v>42.8</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>45.5</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>50.7</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>51.5</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>52.3</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>56.9</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>59.6</v>
       </c>
-      <c r="J9" t="n">
-        <v>62.0</v>
-      </c>
-      <c r="K9" t="n" s="2">
-        <v>44733.0</v>
+      <c r="J9">
+        <v>62</v>
+      </c>
+      <c r="K9" s="1">
+        <v>44733</v>
       </c>
       <c r="L9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>20</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>44.7</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>46.5</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>48.4</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>52.8</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>54.1</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>55.1</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>58.4</v>
       </c>
-      <c r="I10" t="n">
-        <v>61.0</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="I10">
+        <v>61</v>
+      </c>
+      <c r="J10">
         <v>63.2</v>
       </c>
-      <c r="K10" t="n" s="2">
-        <v>44733.0</v>
+      <c r="K10" s="1">
+        <v>44733</v>
       </c>
       <c r="L10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>21</v>
       </c>
-      <c r="B11" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="C11" t="n">
+      <c r="B11">
+        <v>40</v>
+      </c>
+      <c r="C11">
         <v>43.7</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>47.7</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>52.3</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>53.4</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>54.9</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>58.6</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>62.3</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>66.5</v>
       </c>
-      <c r="K11" t="n" s="2">
-        <v>44733.0</v>
+      <c r="K11" s="1">
+        <v>44733</v>
       </c>
       <c r="L11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="n">
+        <v>26</v>
+      </c>
+      <c r="B12">
         <v>34.1</v>
       </c>
-      <c r="C12" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="C12">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="D12">
         <v>46.2</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>47.3</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>48.9</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>50.2</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>51.6</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>56.6</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>60.3</v>
       </c>
-      <c r="K12" t="n" s="2">
-        <v>44733.0</v>
+      <c r="K12" s="1">
+        <v>44733</v>
       </c>
       <c r="L12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>38.4</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>45.1</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>49.5</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>48.8</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>50.7</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>52.3</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>50.5</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>55.6</v>
       </c>
-      <c r="J13" t="n">
-        <v>63.0</v>
-      </c>
-      <c r="K13" t="n" s="2">
-        <v>44765.0</v>
+      <c r="J13">
+        <v>63</v>
+      </c>
+      <c r="K13" s="1">
+        <v>44765</v>
       </c>
       <c r="L13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" t="n">
-        <v>38.0</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="B14">
+        <v>38</v>
+      </c>
+      <c r="C14">
         <v>44.2</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>47.7</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>51.8</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>53.1</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>54.2</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>57.5</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>61.1</v>
       </c>
-      <c r="J14" t="n">
-        <v>66.1</v>
-      </c>
-      <c r="K14" t="n" s="2">
-        <v>44765.0</v>
+      <c r="J14">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="K14" s="1">
+        <v>44765</v>
       </c>
       <c r="L14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>17</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>42.2</v>
       </c>
-      <c r="C15" t="n">
-        <v>46.0</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="C15">
+        <v>46</v>
+      </c>
+      <c r="D15">
         <v>49.7</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>51.4</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>52.5</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>54.2</v>
       </c>
-      <c r="H15" t="n">
-        <v>54.0</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="H15">
+        <v>54</v>
+      </c>
+      <c r="I15">
         <v>58.3</v>
       </c>
-      <c r="J15" t="n">
-        <v>64.1</v>
-      </c>
-      <c r="K15" t="n" s="2">
-        <v>44765.0</v>
+      <c r="J15">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="K15" s="1">
+        <v>44765</v>
       </c>
       <c r="L15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>12</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>42.5</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>46.1</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>49.2</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>51.4</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>52.4</v>
       </c>
-      <c r="G16" t="n">
-        <v>54.0</v>
-      </c>
-      <c r="H16" t="n">
+      <c r="G16">
+        <v>54</v>
+      </c>
+      <c r="H16">
         <v>54.1</v>
       </c>
-      <c r="I16" t="n">
-        <v>58.0</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="I16">
+        <v>58</v>
+      </c>
+      <c r="J16">
         <v>62.8</v>
       </c>
-      <c r="K16" t="n" s="2">
-        <v>44768.0</v>
+      <c r="K16" s="1">
+        <v>44768</v>
       </c>
       <c r="L16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>13</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>45.7</v>
       </c>
-      <c r="C17" t="n">
-        <v>48.0</v>
-      </c>
-      <c r="D17" t="n">
+      <c r="C17">
+        <v>48</v>
+      </c>
+      <c r="D17">
         <v>49.7</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>52.4</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>53.2</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>54.6</v>
       </c>
-      <c r="H17" t="n">
-        <v>55.0</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="H17">
+        <v>55</v>
+      </c>
+      <c r="I17">
         <v>57.8</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>62.1</v>
       </c>
-      <c r="K17" t="n" s="2">
-        <v>44768.0</v>
+      <c r="K17" s="1">
+        <v>44768</v>
       </c>
       <c r="L17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>14</v>
       </c>
-      <c r="B18" t="n">
-        <v>45.0</v>
-      </c>
-      <c r="C18" t="n">
+      <c r="B18">
+        <v>45</v>
+      </c>
+      <c r="C18">
         <v>47.8</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>50.2</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>51.7</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>52.7</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>53.8</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>54.8</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>57.2</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18">
         <v>60.5</v>
       </c>
-      <c r="K18" t="n" s="2">
-        <v>44768.0</v>
+      <c r="K18" s="1">
+        <v>44768</v>
       </c>
       <c r="L18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>15</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>44.2</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>47.4</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>51.4</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>52.6</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>53.7</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>54.7</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>54.1</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>59.2</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19">
         <v>62.3</v>
       </c>
-      <c r="K19" t="n" s="2">
-        <v>44768.0</v>
+      <c r="K19" s="1">
+        <v>44768</v>
       </c>
       <c r="L19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>16</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>44.5</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>46.2</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>48.2</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>52.9</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>54.5</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>55.8</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>58.7</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>61.8</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20">
         <v>65.5</v>
       </c>
-      <c r="K20" t="n" s="2">
-        <v>44768.0</v>
+      <c r="K20" s="1">
+        <v>44768</v>
       </c>
       <c r="L20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>17</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>42.3</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>44.1</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>46.5</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>51.6</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>52.4</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>53.2</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>57.4</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>59.7</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21">
         <v>62.1</v>
       </c>
-      <c r="K21" t="n" s="2">
-        <v>44768.0</v>
+      <c r="K21" s="1">
+        <v>44768</v>
       </c>
       <c r="L21" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>18</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>47.2</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>48.5</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>50.2</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>50.9</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>51.8</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>52.5</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>52.9</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>54.5</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22">
         <v>55.6</v>
       </c>
-      <c r="K22" t="n" s="2">
-        <v>44768.0</v>
+      <c r="K22" s="1">
+        <v>44768</v>
       </c>
       <c r="L22" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>19</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>41.8</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>46.4</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>49.2</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>51.2</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>52.2</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>53.6</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>54.8</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>57.5</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23">
         <v>63.5</v>
       </c>
-      <c r="K23" t="n" s="2">
-        <v>44768.0</v>
+      <c r="K23" s="1">
+        <v>44768</v>
       </c>
       <c r="L23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>20</v>
       </c>
-      <c r="B24" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="C24" t="n">
+      <c r="B24">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="C24">
         <v>44.1</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>47.9</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>54.2</v>
       </c>
-      <c r="F24" t="n">
-        <v>56.0</v>
-      </c>
-      <c r="G24" t="n">
+      <c r="F24">
+        <v>56</v>
+      </c>
+      <c r="G24">
         <v>58.9</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>60.7</v>
       </c>
-      <c r="I24" t="n">
-        <v>66.6</v>
-      </c>
-      <c r="J24" t="n">
+      <c r="I24">
+        <v>66.599999999999994</v>
+      </c>
+      <c r="J24">
         <v>76.8</v>
       </c>
-      <c r="K24" t="n" s="2">
-        <v>44768.0</v>
+      <c r="K24" s="1">
+        <v>44768</v>
       </c>
       <c r="L24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>21</v>
       </c>
-      <c r="B25" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="C25" t="n">
+      <c r="B25">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="C25">
         <v>43.9</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>47.4</v>
       </c>
-      <c r="E25" t="n">
-        <v>52.0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>53.0</v>
-      </c>
-      <c r="G25" t="n">
+      <c r="E25">
+        <v>52</v>
+      </c>
+      <c r="F25">
+        <v>53</v>
+      </c>
+      <c r="G25">
         <v>55.1</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>56.7</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>60.9</v>
       </c>
-      <c r="J25" t="n">
-        <v>69.4</v>
-      </c>
-      <c r="K25" t="n" s="2">
-        <v>44768.0</v>
+      <c r="J25">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="K25" s="1">
+        <v>44768</v>
       </c>
       <c r="L25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" t="n">
+        <v>26</v>
+      </c>
+      <c r="B26">
         <v>44.4</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>47.6</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>50.2</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>52.5</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>53.5</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>55.1</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26">
         <v>55.6</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>58.9</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26">
         <v>63.3</v>
       </c>
-      <c r="K26" t="n" s="2">
-        <v>44768.0</v>
+      <c r="K26" s="1">
+        <v>44768</v>
       </c>
       <c r="L26" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>12</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>43.2</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>45.2</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>47.4</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>48.2</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>49.2</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>50.2</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27">
         <v>50.8</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27">
         <v>52.6</v>
       </c>
-      <c r="J27" t="n">
-        <v>54.0</v>
-      </c>
-      <c r="K27" t="n" s="2">
-        <v>44772.0</v>
+      <c r="J27">
+        <v>54</v>
+      </c>
+      <c r="K27" s="1">
+        <v>44772</v>
       </c>
       <c r="L27" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>14</v>
       </c>
-      <c r="B28" t="n">
-        <v>23.0</v>
-      </c>
-      <c r="C28" t="n">
+      <c r="B28">
+        <v>23</v>
+      </c>
+      <c r="C28">
         <v>26.5</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>39.1</v>
       </c>
-      <c r="E28" t="n">
-        <v>36.0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="E28">
+        <v>36</v>
+      </c>
+      <c r="F28">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="G28">
         <v>42.8</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28">
         <v>55.8</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28">
         <v>65.5</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28">
         <v>76.5</v>
       </c>
-      <c r="K28" t="n" s="2">
-        <v>44772.0</v>
+      <c r="K28" s="1">
+        <v>44772</v>
       </c>
       <c r="L28" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>17</v>
       </c>
-      <c r="B29" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="C29" t="n">
-        <v>44.0</v>
-      </c>
-      <c r="D29" t="n">
+      <c r="B29">
+        <v>40</v>
+      </c>
+      <c r="C29">
+        <v>44</v>
+      </c>
+      <c r="D29">
         <v>48.9</v>
       </c>
-      <c r="E29" t="n">
-        <v>52.0</v>
-      </c>
-      <c r="F29" t="n">
+      <c r="E29">
+        <v>52</v>
+      </c>
+      <c r="F29">
         <v>52.9</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29">
         <v>53.8</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29">
         <v>56.7</v>
       </c>
-      <c r="I29" t="n">
-        <v>61.0</v>
-      </c>
-      <c r="J29" t="n">
+      <c r="I29">
+        <v>61</v>
+      </c>
+      <c r="J29">
         <v>64.7</v>
       </c>
-      <c r="K29" t="n" s="2">
-        <v>44772.0</v>
+      <c r="K29" s="1">
+        <v>44772</v>
       </c>
       <c r="L29" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>12</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>44.2</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>46.8</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>49.2</v>
       </c>
-      <c r="E30" t="n">
-        <v>49.0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="G30" t="n">
+      <c r="E30">
+        <v>49</v>
+      </c>
+      <c r="F30">
+        <v>50</v>
+      </c>
+      <c r="G30">
         <v>50.6</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30">
         <v>51.5</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30">
         <v>52.7</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30">
         <v>54.4</v>
       </c>
-      <c r="K30" t="n" s="2">
-        <v>44775.0</v>
+      <c r="K30" s="1">
+        <v>44775</v>
       </c>
       <c r="L30" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>14</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>25.5</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>38.5</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>46.5</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>46.2</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>48.1</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31">
         <v>49.8</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31">
         <v>51.1</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31">
         <v>57.6</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31">
         <v>67.3</v>
       </c>
-      <c r="K31" t="n" s="2">
-        <v>44775.0</v>
+      <c r="K31" s="1">
+        <v>44775</v>
       </c>
       <c r="L31" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>17</v>
       </c>
-      <c r="B32" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="C32" t="n">
+      <c r="B32">
+        <v>40</v>
+      </c>
+      <c r="C32">
         <v>43.1</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>46.5</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>50.2</v>
       </c>
-      <c r="F32" t="n">
-        <v>51.0</v>
-      </c>
-      <c r="G32" t="n">
+      <c r="F32">
+        <v>51</v>
+      </c>
+      <c r="G32">
         <v>51.9</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32">
         <v>54.8</v>
       </c>
-      <c r="I32" t="n">
-        <v>58.0</v>
-      </c>
-      <c r="J32" t="n">
+      <c r="I32">
+        <v>58</v>
+      </c>
+      <c r="J32">
         <v>62.2</v>
       </c>
-      <c r="K32" t="n" s="2">
-        <v>44775.0</v>
+      <c r="K32" s="1">
+        <v>44775</v>
       </c>
       <c r="L32" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>12</v>
       </c>
-      <c r="B33" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="C33" t="n">
+      <c r="B33">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="C33">
         <v>41.7</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>44.7</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>48.1</v>
       </c>
-      <c r="F33" t="n">
-        <v>49.0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="H33" t="n">
+      <c r="F33">
+        <v>49</v>
+      </c>
+      <c r="G33">
+        <v>50</v>
+      </c>
+      <c r="H33">
         <v>52.5</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33">
         <v>55.6</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J33">
         <v>59.2</v>
       </c>
-      <c r="K33" t="n" s="2">
-        <v>45063.0</v>
+      <c r="K33" s="1">
+        <v>45063</v>
       </c>
       <c r="L33" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>14</v>
       </c>
-      <c r="B34" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="C34" t="n">
+      <c r="B34">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="C34">
         <v>42.7</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>45.7</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>47.5</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34">
         <v>48.5</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34">
         <v>49.6</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34">
         <v>50.3</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34">
         <v>53.6</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J34">
         <v>58.3</v>
       </c>
-      <c r="K34" t="n" s="2">
-        <v>45063.0</v>
+      <c r="K34" s="1">
+        <v>45063</v>
       </c>
       <c r="L34" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>17</v>
       </c>
-      <c r="B35" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="C35" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="D35" t="n">
+      <c r="B35">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="C35">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="D35">
         <v>43.5</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35">
         <v>48.8</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35">
         <v>49.7</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35">
         <v>50.8</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35">
         <v>54.7</v>
       </c>
-      <c r="I35" t="n">
-        <v>58.0</v>
-      </c>
-      <c r="J35" t="n">
+      <c r="I35">
+        <v>58</v>
+      </c>
+      <c r="J35">
         <v>61.4</v>
       </c>
-      <c r="K35" t="n" s="2">
-        <v>45063.0</v>
+      <c r="K35" s="1">
+        <v>45063</v>
       </c>
       <c r="L35" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>12</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>43.2</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>45.5</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>47.5</v>
       </c>
-      <c r="E36" t="n">
-        <v>48.0</v>
-      </c>
-      <c r="F36" t="n">
+      <c r="E36">
+        <v>48</v>
+      </c>
+      <c r="F36">
         <v>48.8</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36">
         <v>49.6</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36">
         <v>50.4</v>
       </c>
-      <c r="I36" t="n">
-        <v>52.0</v>
-      </c>
-      <c r="J36" t="n">
+      <c r="I36">
+        <v>52</v>
+      </c>
+      <c r="J36">
         <v>53.7</v>
       </c>
-      <c r="K36" t="n" s="2">
-        <v>45077.0</v>
+      <c r="K36" s="1">
+        <v>45077</v>
       </c>
       <c r="L36" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>14</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>42.3</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>43.5</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>45.2</v>
       </c>
-      <c r="E37" t="n">
-        <v>48.0</v>
-      </c>
-      <c r="F37" t="n">
+      <c r="E37">
+        <v>48</v>
+      </c>
+      <c r="F37">
         <v>48.4</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37">
         <v>48.8</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H37">
         <v>51.1</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I37">
         <v>52.7</v>
       </c>
-      <c r="J37" t="n">
-        <v>54.0</v>
-      </c>
-      <c r="K37" t="n" s="2">
-        <v>45077.0</v>
+      <c r="J37">
+        <v>54</v>
+      </c>
+      <c r="K37" s="1">
+        <v>45077</v>
       </c>
       <c r="L37" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>17</v>
       </c>
-      <c r="B38" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="C38" t="n">
+      <c r="B38">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="C38">
         <v>40.9</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>43.2</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38">
         <v>48.6</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>49.3</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38">
         <v>49.9</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38">
         <v>55.1</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38">
         <v>56.7</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J38">
         <v>58.8</v>
       </c>
-      <c r="K38" t="n" s="2">
-        <v>45077.0</v>
+      <c r="K38" s="1">
+        <v>45077</v>
       </c>
       <c r="L38" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>12</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39">
         <v>41.5</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>43.7</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>48.4</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>48.1</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>49.3</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39">
         <v>50.5</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39">
         <v>52.4</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39">
         <v>54.3</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J39">
         <v>55.9</v>
       </c>
-      <c r="K39" t="n" s="2">
-        <v>45090.0</v>
+      <c r="K39" s="1">
+        <v>45090</v>
       </c>
       <c r="L39" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>13</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>39.5</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>42.6</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>45.5</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40">
         <v>49.8</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40">
         <v>50.5</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40">
         <v>51.2</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40">
         <v>55.1</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40">
         <v>57.4</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J40">
         <v>59.8</v>
       </c>
-      <c r="K40" t="n" s="2">
-        <v>45090.0</v>
+      <c r="K40" s="1">
+        <v>45090</v>
       </c>
       <c r="L40" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>14</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41">
         <v>37.1</v>
       </c>
-      <c r="C41" t="n">
-        <v>41.0</v>
-      </c>
-      <c r="D41" t="n">
+      <c r="C41">
+        <v>41</v>
+      </c>
+      <c r="D41">
         <v>44.7</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>45.7</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41">
         <v>46.5</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G41">
         <v>47.3</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H41">
         <v>48.5</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41">
         <v>51.8</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J41">
         <v>54.3</v>
       </c>
-      <c r="K41" t="n" s="2">
-        <v>45090.0</v>
+      <c r="K41" s="1">
+        <v>45090</v>
       </c>
       <c r="L41" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>15</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42">
         <v>44.7</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>46.2</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>48.9</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42">
         <v>48.9</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42">
         <v>49.7</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G42">
         <v>50.7</v>
       </c>
-      <c r="H42" t="n">
+      <c r="H42">
         <v>51.4</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I42">
         <v>52.8</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J42">
         <v>54.2</v>
       </c>
-      <c r="K42" t="n" s="2">
-        <v>45090.0</v>
+      <c r="K42" s="1">
+        <v>45090</v>
       </c>
       <c r="L42" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>16</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43">
         <v>41.3</v>
       </c>
-      <c r="C43" t="n">
-        <v>45.0</v>
-      </c>
-      <c r="D43" t="n">
+      <c r="C43">
+        <v>45</v>
+      </c>
+      <c r="D43">
         <v>48.7</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43">
         <v>49.1</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43">
         <v>50.1</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43">
         <v>51.1</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43">
         <v>52.2</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43">
         <v>54.7</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J43">
         <v>57.1</v>
       </c>
-      <c r="K43" t="n" s="2">
-        <v>45090.0</v>
+      <c r="K43" s="1">
+        <v>45090</v>
       </c>
       <c r="L43" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>17</v>
       </c>
-      <c r="B44" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="C44" t="n">
+      <c r="B44">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="C44">
         <v>39.6</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>43.7</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44">
         <v>49.2</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44">
         <v>50.5</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44">
         <v>51.7</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44">
         <v>57.4</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I44">
         <v>60.2</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J44">
         <v>62.7</v>
       </c>
-      <c r="K44" t="n" s="2">
-        <v>45090.0</v>
+      <c r="K44" s="1">
+        <v>45090</v>
       </c>
       <c r="L44" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>18</v>
       </c>
-      <c r="B45" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="C45" t="n">
+      <c r="B45">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="C45">
         <v>40.4</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>45.2</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>44.4</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>45.9</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G45">
         <v>47.4</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H45">
         <v>48.9</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45">
         <v>51.1</v>
       </c>
-      <c r="J45" t="n">
-        <v>53.0</v>
-      </c>
-      <c r="K45" t="n" s="2">
-        <v>45090.0</v>
+      <c r="J45">
+        <v>53</v>
+      </c>
+      <c r="K45" s="1">
+        <v>45090</v>
       </c>
       <c r="L45" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>19</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46">
         <v>30.1</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>41.1</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>48.7</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46">
         <v>47.3</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46">
         <v>49.4</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G46">
         <v>50.7</v>
       </c>
-      <c r="H46" t="n">
+      <c r="H46">
         <v>52.1</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I46">
         <v>57.6</v>
       </c>
-      <c r="J46" t="n">
-        <v>65.6</v>
-      </c>
-      <c r="K46" t="n" s="2">
-        <v>45090.0</v>
+      <c r="J46">
+        <v>65.599999999999994</v>
+      </c>
+      <c r="K46" s="1">
+        <v>45090</v>
       </c>
       <c r="L46" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>20</v>
       </c>
-      <c r="B47" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="C47" t="n">
+      <c r="B47">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="C47">
         <v>38.5</v>
       </c>
-      <c r="D47" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="E47" t="n">
+      <c r="D47">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="E47">
         <v>49.6</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47">
         <v>50.3</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47">
         <v>51.3</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47">
         <v>58.5</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I47">
         <v>60.5</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J47">
         <v>62.7</v>
       </c>
-      <c r="K47" t="n" s="2">
-        <v>45090.0</v>
+      <c r="K47" s="1">
+        <v>45090</v>
       </c>
       <c r="L47" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>21</v>
       </c>
-      <c r="B48" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="C48" t="n">
+      <c r="B48">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="C48">
         <v>41.9</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>43.2</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48">
         <v>50.4</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48">
         <v>50.9</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48">
         <v>51.3</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H48">
         <v>57.3</v>
       </c>
-      <c r="I48" t="n">
+      <c r="I48">
         <v>58.8</v>
       </c>
-      <c r="J48" t="n">
+      <c r="J48">
         <v>60.2</v>
       </c>
-      <c r="K48" t="n" s="2">
-        <v>45090.0</v>
+      <c r="K48" s="1">
+        <v>45090</v>
       </c>
       <c r="L48" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>22</v>
-      </c>
-      <c r="B49" t="n">
-        <v>33.0</v>
-      </c>
-      <c r="C49" t="n">
+        <v>26</v>
+      </c>
+      <c r="B49">
+        <v>33</v>
+      </c>
+      <c r="C49">
         <v>40.9</v>
       </c>
-      <c r="D49" t="n">
-        <v>46.0</v>
-      </c>
-      <c r="E49" t="n">
+      <c r="D49">
+        <v>46</v>
+      </c>
+      <c r="E49">
         <v>46.9</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49">
         <v>48.7</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G49">
         <v>50.3</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H49">
         <v>53.4</v>
       </c>
-      <c r="I49" t="n">
+      <c r="I49">
         <v>56.3</v>
       </c>
-      <c r="J49" t="n">
+      <c r="J49">
         <v>60.8</v>
       </c>
-      <c r="K49" t="n" s="2">
-        <v>45090.0</v>
+      <c r="K49" s="1">
+        <v>45090</v>
       </c>
       <c r="L49" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>12</v>
       </c>
-      <c r="B50" t="n">
-        <v>23.0</v>
-      </c>
-      <c r="C50" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="D50" t="n">
+      <c r="B50">
+        <v>23</v>
+      </c>
+      <c r="C50">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="D50">
         <v>47.7</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50">
         <v>41.3</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50">
         <v>46.1</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50">
         <v>49.4</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H50">
         <v>48.9</v>
       </c>
-      <c r="I50" t="n">
+      <c r="I50">
         <v>54.9</v>
       </c>
-      <c r="J50" t="n">
+      <c r="J50">
         <v>64.8</v>
       </c>
-      <c r="K50" t="n" s="2">
-        <v>45128.0</v>
+      <c r="K50" s="1">
+        <v>45128</v>
       </c>
       <c r="L50" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>14</v>
       </c>
-      <c r="B51" t="n">
-        <v>23.0</v>
-      </c>
-      <c r="C51" t="n">
+      <c r="B51">
+        <v>23</v>
+      </c>
+      <c r="C51">
         <v>29.1</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51">
         <v>44.7</v>
       </c>
-      <c r="E51" t="n">
-        <v>41.0</v>
-      </c>
-      <c r="F51" t="n">
+      <c r="E51">
+        <v>41</v>
+      </c>
+      <c r="F51">
         <v>44.2</v>
       </c>
-      <c r="G51" t="n">
-        <v>48.0</v>
-      </c>
-      <c r="H51" t="n">
+      <c r="G51">
+        <v>48</v>
+      </c>
+      <c r="H51">
         <v>52.4</v>
       </c>
-      <c r="I51" t="n">
+      <c r="I51">
         <v>59.7</v>
       </c>
-      <c r="J51" t="n">
+      <c r="J51">
         <v>69.2</v>
       </c>
-      <c r="K51" t="n" s="2">
-        <v>45128.0</v>
+      <c r="K51" s="1">
+        <v>45128</v>
       </c>
       <c r="L51" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>17</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52">
         <v>46.9</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>48.6</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52">
         <v>50.6</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52">
         <v>51.5</v>
       </c>
-      <c r="F52" t="n">
-        <v>52.0</v>
-      </c>
-      <c r="G52" t="n">
+      <c r="F52">
+        <v>52</v>
+      </c>
+      <c r="G52">
         <v>52.5</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H52">
         <v>53.8</v>
       </c>
-      <c r="I52" t="n">
+      <c r="I52">
         <v>54.9</v>
       </c>
-      <c r="J52" t="n">
+      <c r="J52">
         <v>56.5</v>
       </c>
-      <c r="K52" t="n" s="2">
-        <v>45128.0</v>
+      <c r="K52" s="1">
+        <v>45128</v>
       </c>
       <c r="L52" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>12</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53">
         <v>36.5</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>43.3</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53">
         <v>48.7</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53">
         <v>47.7</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53">
         <v>49.5</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G53">
         <v>50.8</v>
       </c>
-      <c r="H53" t="n">
-        <v>51.0</v>
-      </c>
-      <c r="I53" t="n">
+      <c r="H53">
+        <v>51</v>
+      </c>
+      <c r="I53">
         <v>54.6</v>
       </c>
-      <c r="J53" t="n">
+      <c r="J53">
         <v>58.8</v>
       </c>
-      <c r="K53" t="n" s="2">
-        <v>45130.0</v>
+      <c r="K53" s="1">
+        <v>45130</v>
       </c>
       <c r="L53" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>13</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54">
         <v>42.5</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>44.3</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54">
         <v>46.2</v>
       </c>
-      <c r="E54" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="F54" t="n">
+      <c r="E54">
+        <v>50</v>
+      </c>
+      <c r="F54">
         <v>50.5</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G54">
         <v>50.9</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H54">
         <v>54.6</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I54">
         <v>55.9</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J54">
         <v>57.4</v>
       </c>
-      <c r="K54" t="n" s="2">
-        <v>45130.0</v>
+      <c r="K54" s="1">
+        <v>45130</v>
       </c>
       <c r="L54" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>14</v>
       </c>
-      <c r="B55" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="C55" t="n">
+      <c r="B55">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="C55">
         <v>44.1</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55">
         <v>47.7</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55">
         <v>48.3</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55">
         <v>49.6</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G55">
         <v>50.7</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H55">
         <v>52.8</v>
       </c>
-      <c r="I55" t="n">
-        <v>55.0</v>
-      </c>
-      <c r="J55" t="n">
+      <c r="I55">
+        <v>55</v>
+      </c>
+      <c r="J55">
         <v>57.8</v>
       </c>
-      <c r="K55" t="n" s="2">
-        <v>45130.0</v>
+      <c r="K55" s="1">
+        <v>45130</v>
       </c>
       <c r="L55" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>15</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56">
         <v>38.5</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56">
         <v>45.6</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56">
         <v>49.2</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56">
         <v>50.2</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56">
         <v>51.1</v>
       </c>
-      <c r="G56" t="n">
-        <v>52.0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>53.0</v>
-      </c>
-      <c r="I56" t="n">
+      <c r="G56">
+        <v>52</v>
+      </c>
+      <c r="H56">
+        <v>53</v>
+      </c>
+      <c r="I56">
         <v>55.8</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J56">
         <v>60.7</v>
       </c>
-      <c r="K56" t="n" s="2">
-        <v>45130.0</v>
+      <c r="K56" s="1">
+        <v>45130</v>
       </c>
       <c r="L56" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>16</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57">
         <v>38.5</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57">
         <v>42.4</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57">
         <v>49.2</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57">
         <v>50.4</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57">
         <v>51.5</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G57">
         <v>53.1</v>
       </c>
-      <c r="H57" t="n">
+      <c r="H57">
         <v>51.9</v>
       </c>
-      <c r="I57" t="n">
+      <c r="I57">
         <v>59.7</v>
       </c>
-      <c r="J57" t="n">
-        <v>64.6</v>
-      </c>
-      <c r="K57" t="n" s="2">
-        <v>45130.0</v>
+      <c r="J57">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="K57" s="1">
+        <v>45130</v>
       </c>
       <c r="L57" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>17</v>
       </c>
-      <c r="B58" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="C58" t="n">
+      <c r="B58">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="C58">
         <v>41.1</v>
       </c>
-      <c r="D58" t="n">
-        <v>44.0</v>
-      </c>
-      <c r="E58" t="n">
+      <c r="D58">
+        <v>44</v>
+      </c>
+      <c r="E58">
         <v>49.7</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58">
         <v>50.6</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G58">
         <v>51.5</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H58">
         <v>56.9</v>
       </c>
-      <c r="I58" t="n">
+      <c r="I58">
         <v>59.2</v>
       </c>
-      <c r="J58" t="n">
+      <c r="J58">
         <v>62.3</v>
       </c>
-      <c r="K58" t="n" s="2">
-        <v>45130.0</v>
+      <c r="K58" s="1">
+        <v>45130</v>
       </c>
       <c r="L58" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>18</v>
       </c>
-      <c r="B59" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="C59" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="D59" t="n">
-        <v>46.0</v>
-      </c>
-      <c r="E59" t="n">
+      <c r="B59">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="C59">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="D59">
+        <v>46</v>
+      </c>
+      <c r="E59">
         <v>46.1</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59">
         <v>47.7</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G59">
         <v>49.1</v>
       </c>
-      <c r="H59" t="n">
+      <c r="H59">
         <v>50.9</v>
       </c>
-      <c r="I59" t="n">
+      <c r="I59">
         <v>54.5</v>
       </c>
-      <c r="J59" t="n">
+      <c r="J59">
         <v>57.3</v>
       </c>
-      <c r="K59" t="n" s="2">
-        <v>45130.0</v>
+      <c r="K59" s="1">
+        <v>45130</v>
       </c>
       <c r="L59" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>19</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B60">
         <v>45.7</v>
       </c>
-      <c r="C60" t="n">
-        <v>49.0</v>
-      </c>
-      <c r="D60" t="n">
+      <c r="C60">
+        <v>49</v>
+      </c>
+      <c r="D60">
         <v>52.1</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60">
         <v>52.4</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60">
         <v>53.7</v>
       </c>
-      <c r="G60" t="n">
+      <c r="G60">
         <v>55.7</v>
       </c>
-      <c r="H60" t="n">
+      <c r="H60">
         <v>53.5</v>
       </c>
-      <c r="I60" t="n">
+      <c r="I60">
         <v>57.1</v>
       </c>
-      <c r="J60" t="n">
+      <c r="J60">
         <v>62.1</v>
       </c>
-      <c r="K60" t="n" s="2">
-        <v>45130.0</v>
+      <c r="K60" s="1">
+        <v>45130</v>
       </c>
       <c r="L60" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>20</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B61">
         <v>41.5</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61">
         <v>44.9</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>48.7</v>
       </c>
-      <c r="E61" t="n">
-        <v>53.0</v>
-      </c>
-      <c r="F61" t="n">
+      <c r="E61">
+        <v>53</v>
+      </c>
+      <c r="F61">
         <v>54.4</v>
       </c>
-      <c r="G61" t="n">
+      <c r="G61">
         <v>55.7</v>
       </c>
-      <c r="H61" t="n">
+      <c r="H61">
         <v>59.9</v>
       </c>
-      <c r="I61" t="n">
+      <c r="I61">
         <v>62.4</v>
       </c>
-      <c r="J61" t="n">
+      <c r="J61">
         <v>64.8</v>
       </c>
-      <c r="K61" t="n" s="2">
-        <v>45130.0</v>
+      <c r="K61" s="1">
+        <v>45130</v>
       </c>
       <c r="L61" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>21</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B62">
         <v>41.3</v>
       </c>
-      <c r="C62" t="n">
-        <v>43.0</v>
-      </c>
-      <c r="D62" t="n">
+      <c r="C62">
+        <v>43</v>
+      </c>
+      <c r="D62">
         <v>44.7</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62">
         <v>50.8</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62">
         <v>51.5</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G62">
         <v>52.4</v>
       </c>
-      <c r="H62" t="n">
+      <c r="H62">
         <v>56.5</v>
       </c>
-      <c r="I62" t="n">
-        <v>59.0</v>
-      </c>
-      <c r="J62" t="n">
+      <c r="I62">
+        <v>59</v>
+      </c>
+      <c r="J62">
         <v>61.1</v>
       </c>
-      <c r="K62" t="n" s="2">
-        <v>45130.0</v>
+      <c r="K62" s="1">
+        <v>45130</v>
       </c>
       <c r="L62" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="63">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>22</v>
-      </c>
-      <c r="B63" t="n">
+        <v>26</v>
+      </c>
+      <c r="B63">
         <v>36.5</v>
       </c>
-      <c r="C63" t="n">
-        <v>44.0</v>
-      </c>
-      <c r="D63" t="n">
+      <c r="C63">
+        <v>44</v>
+      </c>
+      <c r="D63">
         <v>50.6</v>
       </c>
-      <c r="E63" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="F63" t="n">
+      <c r="E63">
+        <v>50</v>
+      </c>
+      <c r="F63">
         <v>51.3</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G63">
         <v>52.7</v>
       </c>
-      <c r="H63" t="n">
+      <c r="H63">
         <v>54.4</v>
       </c>
-      <c r="I63" t="n">
+      <c r="I63">
         <v>58.2</v>
       </c>
-      <c r="J63" t="n">
+      <c r="J63">
         <v>63.3</v>
       </c>
-      <c r="K63" t="n" s="2">
-        <v>45130.0</v>
+      <c r="K63" s="1">
+        <v>45130</v>
       </c>
       <c r="L63" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>12</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B64">
         <v>38.5</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64">
         <v>44.1</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64">
         <v>48.2</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64">
         <v>46.2</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64">
         <v>48.5</v>
       </c>
-      <c r="G64" t="n">
+      <c r="G64">
         <v>49.8</v>
       </c>
-      <c r="H64" t="n">
+      <c r="H64">
         <v>50.1</v>
       </c>
-      <c r="I64" t="n">
+      <c r="I64">
         <v>52.8</v>
       </c>
-      <c r="J64" t="n">
+      <c r="J64">
         <v>55.4</v>
       </c>
-      <c r="K64" t="n" s="2">
-        <v>45135.0</v>
+      <c r="K64" s="1">
+        <v>45135</v>
       </c>
       <c r="L64" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="65">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>14</v>
       </c>
-      <c r="B65" t="n">
+      <c r="B65">
         <v>28.8</v>
       </c>
-      <c r="C65" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="D65" t="n">
+      <c r="C65">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="D65">
         <v>45.2</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65">
         <v>44.5</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65">
         <v>46.8</v>
       </c>
-      <c r="G65" t="n">
+      <c r="G65">
         <v>48.7</v>
       </c>
-      <c r="H65" t="n">
+      <c r="H65">
         <v>51.5</v>
       </c>
-      <c r="I65" t="n">
+      <c r="I65">
         <v>55.7</v>
       </c>
-      <c r="J65" t="n">
+      <c r="J65">
         <v>61.5</v>
       </c>
-      <c r="K65" t="n" s="2">
-        <v>45135.0</v>
+      <c r="K65" s="1">
+        <v>45135</v>
       </c>
       <c r="L65" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="66">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>17</v>
       </c>
-      <c r="B66" t="n">
-        <v>43.0</v>
-      </c>
-      <c r="C66" t="n">
+      <c r="B66">
+        <v>43</v>
+      </c>
+      <c r="C66">
         <v>46.4</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66">
         <v>50.2</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66">
         <v>51.5</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66">
         <v>52.4</v>
       </c>
-      <c r="G66" t="n">
+      <c r="G66">
         <v>52.9</v>
       </c>
-      <c r="H66" t="n">
+      <c r="H66">
         <v>54.6</v>
       </c>
-      <c r="I66" t="n">
+      <c r="I66">
         <v>57.8</v>
       </c>
-      <c r="J66" t="n">
+      <c r="J66">
         <v>60.9</v>
       </c>
-      <c r="K66" t="n" s="2">
-        <v>45135.0</v>
+      <c r="K66" s="1">
+        <v>45135</v>
       </c>
       <c r="L66" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="67">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>12</v>
       </c>
-      <c r="B67" t="n">
-        <v>23.0</v>
-      </c>
-      <c r="C67" t="n">
+      <c r="B67">
+        <v>23</v>
+      </c>
+      <c r="C67">
         <v>39.5</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67">
         <v>45.7</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67">
         <v>40.4</v>
       </c>
-      <c r="F67" t="n">
-        <v>45.0</v>
-      </c>
-      <c r="G67" t="n">
+      <c r="F67">
+        <v>45</v>
+      </c>
+      <c r="G67">
         <v>46.9</v>
       </c>
-      <c r="H67" t="n">
+      <c r="H67">
         <v>47.3</v>
       </c>
-      <c r="I67" t="n">
+      <c r="I67">
         <v>50.3</v>
       </c>
-      <c r="J67" t="n">
+      <c r="J67">
         <v>58.6</v>
       </c>
-      <c r="K67" t="n" s="2">
-        <v>45138.0</v>
+      <c r="K67" s="1">
+        <v>45138</v>
       </c>
       <c r="L67" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="68">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>14</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B68">
         <v>33.6</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68">
         <v>41.6</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68">
         <v>49.2</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68">
         <v>46.5</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68">
         <v>48.5</v>
       </c>
-      <c r="G68" t="n">
+      <c r="G68">
         <v>50.8</v>
       </c>
-      <c r="H68" t="n">
+      <c r="H68">
         <v>51.9</v>
       </c>
-      <c r="I68" t="n">
+      <c r="I68">
         <v>55.2</v>
       </c>
-      <c r="J68" t="n">
+      <c r="J68">
         <v>60.3</v>
       </c>
-      <c r="K68" t="n" s="2">
-        <v>45138.0</v>
+      <c r="K68" s="1">
+        <v>45138</v>
       </c>
       <c r="L68" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="69">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>17</v>
       </c>
-      <c r="B69" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="C69" t="n">
+      <c r="B69">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="C69">
         <v>41.7</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69">
         <v>44.7</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69">
         <v>48.9</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69">
         <v>49.7</v>
       </c>
-      <c r="G69" t="n">
+      <c r="G69">
         <v>50.3</v>
       </c>
-      <c r="H69" t="n">
-        <v>55.0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>57.0</v>
-      </c>
-      <c r="J69" t="n">
+      <c r="H69">
+        <v>55</v>
+      </c>
+      <c r="I69">
+        <v>57</v>
+      </c>
+      <c r="J69">
         <v>58.9</v>
       </c>
-      <c r="K69" t="n" s="2">
-        <v>45138.0</v>
+      <c r="K69" s="1">
+        <v>45138</v>
       </c>
       <c r="L69" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="70">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>12</v>
       </c>
-      <c r="B70" t="n">
+      <c r="B70">
         <v>30.8</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70">
         <v>40.6</v>
       </c>
-      <c r="D70" t="n">
-        <v>48.0</v>
-      </c>
-      <c r="E70" t="n">
+      <c r="D70">
+        <v>48</v>
+      </c>
+      <c r="E70">
         <v>43.9</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70">
         <v>46.9</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G70">
         <v>49.6</v>
       </c>
-      <c r="H70" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="I70" t="n">
+      <c r="H70">
+        <v>50</v>
+      </c>
+      <c r="I70">
         <v>53.3</v>
       </c>
-      <c r="J70" t="n">
+      <c r="J70">
         <v>57.5</v>
       </c>
-      <c r="K70" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K70" s="1">
+        <v>45180</v>
       </c>
       <c r="L70" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="71">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>13</v>
       </c>
-      <c r="B71" t="n">
+      <c r="B71">
         <v>42.7</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71">
         <v>47.2</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71">
         <v>50.2</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71">
         <v>51.9</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71">
         <v>52.4</v>
       </c>
-      <c r="G71" t="n">
-        <v>53.0</v>
-      </c>
-      <c r="H71" t="n">
+      <c r="G71">
+        <v>53</v>
+      </c>
+      <c r="H71">
         <v>55.2</v>
       </c>
-      <c r="I71" t="n">
+      <c r="I71">
         <v>57.2</v>
       </c>
-      <c r="J71" t="n">
+      <c r="J71">
         <v>60.8</v>
       </c>
-      <c r="K71" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K71" s="1">
+        <v>45180</v>
       </c>
       <c r="L71" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="72">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>14</v>
       </c>
-      <c r="B72" t="n">
+      <c r="B72">
         <v>30.9</v>
       </c>
-      <c r="C72" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="D72" t="n">
+      <c r="C72">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="D72">
         <v>44.7</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72">
         <v>44.8</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72">
         <v>46.8</v>
       </c>
-      <c r="G72" t="n">
+      <c r="G72">
         <v>48.5</v>
       </c>
-      <c r="H72" t="n">
+      <c r="H72">
         <v>50.7</v>
       </c>
-      <c r="I72" t="n">
+      <c r="I72">
         <v>54.2</v>
       </c>
-      <c r="J72" t="n">
+      <c r="J72">
         <v>58.3</v>
       </c>
-      <c r="K72" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K72" s="1">
+        <v>45180</v>
       </c>
       <c r="L72" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="73">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>15</v>
       </c>
-      <c r="B73" t="n">
+      <c r="B73">
         <v>45.9</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73">
         <v>47.6</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73">
         <v>50.2</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73">
         <v>51.5</v>
       </c>
-      <c r="F73" t="n">
-        <v>52.0</v>
-      </c>
-      <c r="G73" t="n">
+      <c r="F73">
+        <v>52</v>
+      </c>
+      <c r="G73">
         <v>52.6</v>
       </c>
-      <c r="H73" t="n">
+      <c r="H73">
         <v>54.4</v>
       </c>
-      <c r="I73" t="n">
+      <c r="I73">
         <v>56.1</v>
       </c>
-      <c r="J73" t="n">
+      <c r="J73">
         <v>57.8</v>
       </c>
-      <c r="K73" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K73" s="1">
+        <v>45180</v>
       </c>
       <c r="L73" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="74">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>16</v>
       </c>
-      <c r="B74" t="n">
+      <c r="B74">
         <v>45.7</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74">
         <v>47.8</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74">
         <v>50.4</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74">
         <v>50.4</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74">
         <v>51.2</v>
       </c>
-      <c r="G74" t="n">
+      <c r="G74">
         <v>52.2</v>
       </c>
-      <c r="H74" t="n">
+      <c r="H74">
         <v>52.9</v>
       </c>
-      <c r="I74" t="n">
+      <c r="I74">
         <v>54.3</v>
       </c>
-      <c r="J74" t="n">
+      <c r="J74">
         <v>55.8</v>
       </c>
-      <c r="K74" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K74" s="1">
+        <v>45180</v>
       </c>
       <c r="L74" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="75">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>17</v>
       </c>
-      <c r="B75" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="C75" t="n">
+      <c r="B75">
+        <v>40</v>
+      </c>
+      <c r="C75">
         <v>42.4</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75">
         <v>44.2</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75">
         <v>49.3</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75">
         <v>50.2</v>
       </c>
-      <c r="G75" t="n">
+      <c r="G75">
         <v>50.9</v>
       </c>
-      <c r="H75" t="n">
+      <c r="H75">
         <v>55.3</v>
       </c>
-      <c r="I75" t="n">
-        <v>57.0</v>
-      </c>
-      <c r="J75" t="n">
+      <c r="I75">
+        <v>57</v>
+      </c>
+      <c r="J75">
         <v>58.9</v>
       </c>
-      <c r="K75" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K75" s="1">
+        <v>45180</v>
       </c>
       <c r="L75" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="76">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>18</v>
       </c>
-      <c r="B76" t="n">
-        <v>23.0</v>
-      </c>
-      <c r="C76" t="n">
+      <c r="B76">
+        <v>23</v>
+      </c>
+      <c r="C76">
         <v>27.7</v>
       </c>
-      <c r="D76" t="n">
-        <v>42.0</v>
-      </c>
-      <c r="E76" t="n">
+      <c r="D76">
+        <v>42</v>
+      </c>
+      <c r="E76">
         <v>37.9</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76">
         <v>41.5</v>
       </c>
-      <c r="G76" t="n">
-        <v>45.0</v>
-      </c>
-      <c r="H76" t="n">
+      <c r="G76">
+        <v>45</v>
+      </c>
+      <c r="H76">
         <v>49.8</v>
       </c>
-      <c r="I76" t="n">
+      <c r="I76">
         <v>55.6</v>
       </c>
-      <c r="J76" t="n">
+      <c r="J76">
         <v>60.6</v>
       </c>
-      <c r="K76" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K76" s="1">
+        <v>45180</v>
       </c>
       <c r="L76" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="77">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>19</v>
       </c>
-      <c r="B77" t="n">
+      <c r="B77">
         <v>28.2</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77">
         <v>41.5</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77">
         <v>50.6</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77">
         <v>50.2</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77">
         <v>52.2</v>
       </c>
-      <c r="G77" t="n">
+      <c r="G77">
         <v>53.5</v>
       </c>
-      <c r="H77" t="n">
+      <c r="H77">
         <v>54.9</v>
       </c>
-      <c r="I77" t="n">
+      <c r="I77">
         <v>60.6</v>
       </c>
-      <c r="J77" t="n">
-        <v>68.6</v>
-      </c>
-      <c r="K77" t="n" s="2">
-        <v>45180.0</v>
+      <c r="J77">
+        <v>68.599999999999994</v>
+      </c>
+      <c r="K77" s="1">
+        <v>45180</v>
       </c>
       <c r="L77" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="78">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>20</v>
       </c>
-      <c r="B78" t="n">
+      <c r="B78">
         <v>41.8</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78">
         <v>43.6</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78">
         <v>45.5</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78">
         <v>51.5</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78">
         <v>52.2</v>
       </c>
-      <c r="G78" t="n">
+      <c r="G78">
         <v>52.9</v>
       </c>
-      <c r="H78" t="n">
+      <c r="H78">
         <v>58.2</v>
       </c>
-      <c r="I78" t="n">
+      <c r="I78">
         <v>60.1</v>
       </c>
-      <c r="J78" t="n">
+      <c r="J78">
         <v>61.9</v>
       </c>
-      <c r="K78" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K78" s="1">
+        <v>45180</v>
       </c>
       <c r="L78" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="79">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>21</v>
       </c>
-      <c r="B79" t="n">
+      <c r="B79">
         <v>42.7</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79">
         <v>44.1</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79">
         <v>45.2</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79">
         <v>50.1</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79">
         <v>50.7</v>
       </c>
-      <c r="G79" t="n">
+      <c r="G79">
         <v>51.3</v>
       </c>
-      <c r="H79" t="n">
+      <c r="H79">
         <v>54.7</v>
       </c>
-      <c r="I79" t="n">
+      <c r="I79">
         <v>56.3</v>
       </c>
-      <c r="J79" t="n">
+      <c r="J79">
         <v>57.6</v>
       </c>
-      <c r="K79" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K79" s="1">
+        <v>45180</v>
       </c>
       <c r="L79" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>26</v>
+      </c>
+      <c r="B80">
         <v>23</v>
       </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>22</v>
-      </c>
-      <c r="B80" t="n">
-        <v>23.0</v>
-      </c>
-      <c r="C80" t="n">
+      <c r="C80">
         <v>32.4</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80">
         <v>50.5</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80">
         <v>44.3</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80">
         <v>48.3</v>
       </c>
-      <c r="G80" t="n">
+      <c r="G80">
         <v>52.5</v>
       </c>
-      <c r="H80" t="n">
+      <c r="H80">
         <v>54.1</v>
       </c>
-      <c r="I80" t="n">
-        <v>67.6</v>
-      </c>
-      <c r="J80" t="n">
+      <c r="I80">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="J80">
         <v>90.6</v>
       </c>
-      <c r="K80" t="n" s="2">
-        <v>45180.0</v>
+      <c r="K80" s="1">
+        <v>45180</v>
       </c>
       <c r="L80" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>